--- a/MsPFM/AIC8822/MsTables/WF_MEASURE_TABLE_20240627_V2.xlsx
+++ b/MsPFM/AIC8822/MsTables/WF_MEASURE_TABLE_20240627_V2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24135" windowHeight="13455"/>
+    <workbookView windowWidth="26670" windowHeight="14040"/>
   </bookViews>
   <sheets>
     <sheet name="PMS" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
     <t>2 2</t>
   </si>
   <si>
-    <t>0 24 1</t>
+    <t>14 24 1</t>
   </si>
   <si>
     <t>NA</t>

--- a/MsPFM/AIC8822/MsTables/WF_MEASURE_TABLE_20240627_V2.xlsx
+++ b/MsPFM/AIC8822/MsTables/WF_MEASURE_TABLE_20240627_V2.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="20">
+  <si>
+    <t>TEST_ENABLE</t>
+  </si>
   <si>
     <t>SETCH</t>
   </si>
@@ -46,6 +49,9 @@
     <t>R_MASK</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>42,58,106,122,138,155</t>
   </si>
   <si>
@@ -59,9 +65,6 @@
   </si>
   <si>
     <t>NA</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>N</t>
@@ -686,9 +689,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1044,286 +1050,299 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="6" max="6" width="11.125" customWidth="1"/>
-    <col min="8" max="8" width="14.5" customWidth="1"/>
-    <col min="9" max="9" width="13.75" customWidth="1"/>
+    <col min="1" max="1" width="17.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="7" max="7" width="11.125" customWidth="1"/>
+    <col min="9" max="9" width="14.5" customWidth="1"/>
+    <col min="10" max="10" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1">
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2">
         <v>20000</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="E3" s="2">
+        <v>20000</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="G3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2">
+        <v>20000</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="H4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1">
-        <v>20000</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1">
-        <v>20000</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="K4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
